--- a/Prompts used for the tutorial.xlsx
+++ b/Prompts used for the tutorial.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D81DB51E-FFE4-4626-A879-F7E616957981}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KhoaLTM\Code\vibecode-seminar\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15347146-8EEF-4363-BA01-03CFFA4CF95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="1770" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,10 +38,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
+    <t xml:space="preserve">PRDとワイヤーフレーム図の内容をもとに、プロトタイプのショッピングアプリを作成してください。作成先は選択済みの「ShoppingApp」フォルダーとします。プロトタイプには、基本的なユースケース機能、シンプルな画面遷移、サンプルデータセット、最低限のスタイリングを実装してください。  
+アプリを作成したら、ワークスペースに「.github/copilot-instructions.md」ファイルを追加してください。その「copilot-instructions.md」には、PRDとワイヤーフレーム各ファイルの内容を貼り付けてください。
+</t>
+  </si>
+  <si>
+    <t>#codebase 「カートに追加」と「詳細」ボタンは近すぎます。少し離してください</t>
+  </si>
+  <si>
     <t xml:space="preserve">私は、vibe codingプロセスを用いて開発するアプリのために、プロダクト要件定義書（PRD）を作成したいと考えています。PRDには、アプリの目的、対象ユーザー、機能、技術要件に関する情報を含めたいです。私のアプリについて、以下のハイレベルなパラメータを定義しています。1 - HTML、CSS、JavaScriptを使用して、クライアントサイドのWebアプリを作成する。2 - 次のWebページを含める：Products、ProductDetails、ShoppingCart、Checkout。3 - ページ間のナビゲーションを可能にする。  
 プロトタイプアプリには基本的な機能を実装し、少数のハイレベルなユースケースを満たしたいです。プロトタイプでは、以下を実装する必要があります：基本的なユースケース機能、シンプルなナビゲーション、サンプルデータセット、基本的なスタイリング。  
 PRDをチャットのコンテキストに追加した上で、GitHub Copilot Agentにプロトタイプアプリの作成を依頼する予定です。GitHub Copilot Agentに、私が思い描くプロトタイプを作成してもらうために、PRDにはどのようなセクションを含めるべきでしょうか？
 </t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t xml:space="preserve">提案していただいたPRDのセクション構成は良さそうです。PRDを作成するうえで役立つ情報を共有します。
@@ -53,34 +67,39 @@
 Checkoutページは、購入する商品のサマリー（商品名、数量、価格）を表示すること。合計金額を明確に表示し、「Process Order（注文処理）」のオプションを提供すること。
 左側のナビゲーションメニューは、ページ間の基本的な移動を提供すること。表示幅が300ピクセル未満になった場合、ナビゲーションバーは1〜2文字の略称を表示する形に折りたたまれること。ナビゲーションバーにより、ユーザーがアプリ内ページ間を移動できるようにすること。
 </t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t xml:space="preserve">あなたが提案したセクション構成と、私が提供した入力情報を使って、VibeCodingPRD.md という名前のMarkdownファイルを作成してください。
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">私のプロトタイプアプリ用に、各Webページとナビゲーションバー（展開時／折りたたみ時）を表すローファイのワイヤーフレーム図（またはテキストベースのレイアウト）を作成できますか？参考として、私が提供したPRDを使用してください。
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">私のプロトタイプアプリ用に、各Webページとナビゲーションバー（展開時／折りたたみ時）を表すローファイのワイヤーフレーム図（各ページはMarkdownファイルで）を作成できますか？参考として、私が提供したPRDを使用してください。
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDとワイヤーフレーム図の内容をもとに、プロトタイプのショッピングアプリを作成してください。作成先は選択済みの「ShoppingApp」フォルダーとします。プロトタイプには、基本的なユースケース機能、シンプルな画面遷移、サンプルデータセット、最低限のスタイリングを実装してください。  
-アプリを作成したら、ワークスペースに「.github/copilot-instructions.md」ファイルを追加してください。その「copilot-instructions.md」には、PRDとワイヤーフレーム各ファイルの内容を貼り付けてください。
-</t>
-  </si>
-  <si>
-    <t>#codebase 「カートに追加」と「詳細」ボタンは近すぎます。少し離してください</t>
+    <rPh sb="62" eb="63">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -127,9 +146,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -167,7 +186,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -273,7 +292,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -415,7 +434,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -424,42 +443,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="99.7109375" customWidth="1"/>
+    <col min="1" max="1" width="99.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="200.25">
+    <row r="1" spans="1:1" ht="225" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="75" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="409.6">
-      <c r="A2" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="49.5">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="49.5">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="99">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>